--- a/Result/profitability/1560.xlsx
+++ b/Result/profitability/1560.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.64</v>
       </c>
       <c r="M2" t="n">
-        <v>2.05875</v>
+        <v>2.25</v>
       </c>
       <c r="N2" t="n">
-        <v>31.28</v>
+        <v>32.52875</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.57</v>
       </c>
       <c r="M3" t="n">
-        <v>1.885</v>
+        <v>2.11625</v>
       </c>
       <c r="N3" t="n">
-        <v>30.205</v>
+        <v>31.35125</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.53</v>
       </c>
       <c r="M4" t="n">
-        <v>1.74625</v>
+        <v>1.9375</v>
       </c>
       <c r="N4" t="n">
-        <v>29.17875</v>
+        <v>30.32125</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.4</v>
       </c>
       <c r="M5" t="n">
-        <v>1.45125</v>
+        <v>1.66</v>
       </c>
       <c r="N5" t="n">
-        <v>26.15</v>
+        <v>27.13875</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.75</v>
       </c>
       <c r="M6" t="n">
-        <v>1.13</v>
+        <v>1.28625</v>
       </c>
       <c r="N6" t="n">
-        <v>20.1825</v>
+        <v>21.14</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.37</v>
       </c>
       <c r="M7" t="n">
-        <v>0.80375</v>
+        <v>0.8312499999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>17.20375</v>
+        <v>17.9375</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.19</v>
       </c>
       <c r="M8" t="n">
-        <v>0.41875</v>
+        <v>0.4875</v>
       </c>
       <c r="N8" t="n">
-        <v>14.9175</v>
+        <v>15.54875</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1560</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>2493</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1494</v>
+      </c>
+      <c r="E75" t="n">
+        <v>998</v>
+      </c>
+      <c r="F75" t="n">
+        <v>40.05</v>
+      </c>
+      <c r="G75" t="n">
+        <v>604</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>24.22%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>61</v>
+      </c>
+      <c r="J75" t="n">
+        <v>664</v>
+      </c>
+      <c r="K75" t="n">
+        <v>523</v>
+      </c>
+      <c r="L75" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="M75" t="n">
+        <v>2.415</v>
+      </c>
+      <c r="N75" t="n">
+        <v>33.20125</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.5500000000000003</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.1870748299319729</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>5.049999999999997</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.1442857142857141</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.9175824175824177</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>7.909999999999997</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.246110765401369</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
